--- a/data/capstone-cluster-sampling-schools.xlsx
+++ b/data/capstone-cluster-sampling-schools.xlsx
@@ -16576,7 +16576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Year 6 students</t>
+          <t>sixth-grade students</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -16610,14 +16610,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D1 TARGET POPULATION: all Year 6 students in the district's 120 state schools.</t>
+          <t>D1 TARGET POPULATION: all sixth-grade students in the district's 120 public schools.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D2 FRAME: there is NO central list of students. There IS a complete list of schools, with roll</t>
+          <t>D2 FRAME: there is NO central list of students. There IS a complete list of schools, with enrollment</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stage 2 draws 25 Year 6 students at random within each selected school. n = 600 students.</t>
+          <t xml:space="preserve">   Stage 2 draws 25 sixth-grade students at random within each selected school. n = 600 students.</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Year 6 roll at that school, from the frame.</t>
+          <t>Sixth-grade enrollment at that school, from the frame.</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A two-stage cluster sample: 24 schools drawn from 120, then 25 Year 6 students within each.</t>
+          <t>A two-stage cluster sample: 24 schools drawn from 120, then 25 sixth-grade students within each.</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The 'truth' sheet holds the real population values, available only because the population is</t>
+          <t>The 'truth' sheet holds the true population values, available only because the population is</t>
         </is>
       </c>
     </row>
